--- a/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 5,96</t>
+          <t>-15,51; 5,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 8,83</t>
+          <t>-14,69; 9,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 8,06</t>
+          <t>-15,53; 7,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 3,35</t>
+          <t>-4,77; 3,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 16,98</t>
+          <t>-34,24; 15,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 19,78</t>
+          <t>-27,04; 21,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 23,83</t>
+          <t>-35,36; 23,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,58</t>
+          <t>-4,81; 3,99</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 6,67</t>
+          <t>-13,05; 5,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 10,44</t>
+          <t>-9,6; 10,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 9,98</t>
+          <t>-7,92; 9,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,5</t>
+          <t>-1,97; 5,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 18,39</t>
+          <t>-29,0; 15,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 22,52</t>
+          <t>-17,46; 22,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 24,46</t>
+          <t>-16,2; 22,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,99</t>
+          <t>-2,04; 5,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 5,97</t>
+          <t>-15,03; 4,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 9,85</t>
+          <t>-10,82; 10,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 5,74</t>
+          <t>-14,87; 4,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,84</t>
+          <t>-2,05; 6,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 14,72</t>
+          <t>-28,82; 10,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 24,79</t>
+          <t>-21,41; 23,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 14,79</t>
+          <t>-31,73; 10,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 6,42</t>
+          <t>-2,14; 6,83</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 7,74</t>
+          <t>-10,23; 8,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 7,51</t>
+          <t>-11,48; 7,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 19,98</t>
+          <t>-0,16; 18,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,73</t>
+          <t>-6,43; 2,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 20,82</t>
+          <t>-22,35; 22,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 18,63</t>
+          <t>-23,51; 19,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 61,28</t>
+          <t>-0,55; 55,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 2,95</t>
+          <t>-6,67; 2,43</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,74</t>
+          <t>-8,11; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,66</t>
+          <t>-6,86; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,87</t>
+          <t>-3,21; 6,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,48</t>
+          <t>-1,85; 2,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 4,4</t>
+          <t>-17,91; 4,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 7,99</t>
+          <t>-13,63; 6,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 14,84</t>
+          <t>-7,5; 16,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,64</t>
+          <t>-1,91; 2,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 5,57</t>
+          <t>-15,59; 6,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 9,47</t>
+          <t>-13,83; 8,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 7,7</t>
+          <t>-15,41; 7,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 3,77</t>
+          <t>-4,64; 3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 15,6</t>
+          <t>-33,14; 16,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 21,27</t>
+          <t>-25,5; 20,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 23,37</t>
+          <t>-35,46; 24,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,99</t>
+          <t>-4,72; 3,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 5,87</t>
+          <t>-12,43; 6,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 10,37</t>
+          <t>-8,63; 10,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 9,25</t>
+          <t>-7,44; 9,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,29</t>
+          <t>-2,22; 5,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 15,28</t>
+          <t>-27,27; 18,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 22,57</t>
+          <t>-15,6; 22,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 22,53</t>
+          <t>-15,61; 23,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 5,79</t>
+          <t>-2,31; 6,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 4,11</t>
+          <t>-14,96; 5,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 10,33</t>
+          <t>-10,91; 9,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 4,29</t>
+          <t>-15,0; 4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,2</t>
+          <t>-2,38; 6,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 10,04</t>
+          <t>-29,44; 12,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 23,91</t>
+          <t>-20,93; 23,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 10,44</t>
+          <t>-32,13; 11,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 6,83</t>
+          <t>-2,5; 6,74</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 8,09</t>
+          <t>-11,01; 7,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 7,95</t>
+          <t>-12,2; 7,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 18,53</t>
+          <t>0,51; 17,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,29</t>
+          <t>-6,2; 2,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 22,72</t>
+          <t>-23,53; 20,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 19,57</t>
+          <t>-24,07; 18,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 55,23</t>
+          <t>0,94; 53,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,43</t>
+          <t>-6,36; 2,95</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,82</t>
+          <t>-7,75; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,27</t>
+          <t>-6,44; 3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,31</t>
+          <t>-3,27; 6,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,37</t>
+          <t>-1,76; 2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 4,36</t>
+          <t>-17,4; 4,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 6,96</t>
+          <t>-12,96; 7,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,33</t>
+          <t>-7,5; 16,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,53</t>
+          <t>-1,84; 2,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_enfcro_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,74%</t>
+          <t>-0,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 6,07</t>
+          <t>-15,88; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 8,9</t>
+          <t>-14,82; 8,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 7,37</t>
+          <t>-15,79; 8,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 3,33</t>
+          <t>-4,46; 3,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 16,55</t>
+          <t>-33,78; 16,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 20,03</t>
+          <t>-27,14; 19,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 24,05</t>
+          <t>-35,42; 23,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,58</t>
+          <t>-4,55; 3,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 6,49</t>
+          <t>-12,03; 6,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 10,29</t>
+          <t>-9,21; 10,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 9,26</t>
+          <t>-6,72; 9,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 5,6</t>
+          <t>-1,84; 5,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 18,42</t>
+          <t>-26,25; 18,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 22,5</t>
+          <t>-16,25; 22,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 23,39</t>
+          <t>-14,49; 24,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,14</t>
+          <t>-1,91; 6,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 5,21</t>
+          <t>-14,61; 5,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 9,77</t>
+          <t>-11,82; 9,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 4,51</t>
+          <t>-14,12; 5,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,12</t>
+          <t>-3,64; 5,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 12,79</t>
+          <t>-28,3; 14,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 23,35</t>
+          <t>-22,7; 24,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 11,74</t>
+          <t>-29,84; 14,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,74</t>
+          <t>-3,82; 5,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,96%</t>
+          <t>-2,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 7,69</t>
+          <t>-10,43; 7,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 7,39</t>
+          <t>-12,14; 7,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 17,85</t>
+          <t>1,0; 19,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 2,65</t>
+          <t>-6,49; 2,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 20,27</t>
+          <t>-22,35; 20,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 18,23</t>
+          <t>-24,18; 18,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 53,99</t>
+          <t>2,18; 61,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 2,95</t>
+          <t>-6,75; 2,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,86</t>
+          <t>-7,88; 1,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 3,53</t>
+          <t>-6,47; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 6,24</t>
+          <t>-3,13; 5,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,34</t>
+          <t>-2,24; 2,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 4,67</t>
+          <t>-17,38; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 7,64</t>
+          <t>-12,77; 7,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 16,02</t>
+          <t>-7,61; 14,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,49</t>
+          <t>-2,34; 2,38</t>
         </is>
       </c>
     </row>
